--- a/public/inputs/y03-english - input.xlsx
+++ b/public/inputs/y03-english - input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C100"/>
+  <dimension ref="A1:C88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unit 1 · Story writing with roald dahl</t>
+          <t>Unit 1 · Danger!</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>(3)1.1: Setting the scene</t>
+          <t>1.1 Listening and speaking</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>(3)1.2: Looking at a setting</t>
+          <t>1.2 Reading and writing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -480,7 +480,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>(3)1.3: Building a picture with words</t>
+          <t>1.3 Reading and speaking</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -493,7 +493,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>(3)1.4: Writing a setting</t>
+          <t>1.4 Grammar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>(3)1.5: Looking at characters</t>
+          <t>1.5 Spelling</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -519,7 +519,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>(3)1.6: What happens next?</t>
+          <t>1.6 Vocabulary</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>(3)1.7: Looking at verbs</t>
+          <t>1.7 Speaking</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -545,7 +545,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>(3)1.8: Speech in texts</t>
+          <t>1.8 Writing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -558,7 +558,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>(3)1.9: Sequencing events</t>
+          <t>1.9 Reading</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -566,12 +566,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Subunit</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>(3)1.1: 0: Planning a story</t>
+          <t>Unit 2 · Staying in touch</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -584,7 +584,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>(3)1.1: 1: Writing a story</t>
+          <t>2.1 Reading and speaking</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -597,7 +597,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>(3)1.1: 2: Improving your story</t>
+          <t>2.2 Speaking and writing</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -605,12 +605,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Subunit</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Unit 2 · Let's have a party</t>
+          <t>2.3 Spelling and vocabulary</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -623,7 +623,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>(3)2.1: Looking for celebrations</t>
+          <t>2.4 Grammar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -636,7 +636,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>(3)2.1: 1: Writing instructions</t>
+          <t>2.5 Reading and speaking</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>(3)2.1: 2: Improving your instructions</t>
+          <t>2.6 Writing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -662,7 +662,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>(3)2.2: Writing lists</t>
+          <t>2.7 Spelling</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -670,12 +670,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Subunit</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>(3)2.3: Fiction or non-fiction?</t>
+          <t>Unit 3 · Bugs</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -688,7 +688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>(3)2.4: Following instructions</t>
+          <t>3.1 Reading and speaking</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -701,7 +701,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>(3)2.5: Writing an invitation</t>
+          <t>3.2 Listening and speaking</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -714,7 +714,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>(3)2.6: Following and writing instructions</t>
+          <t>3.3 Reading and writing</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>(3)2.7: Contents pages and indexes</t>
+          <t>3.4 Spelling</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -740,7 +740,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>(3)2.8: Making lists</t>
+          <t>3.5 Vocabulary</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -753,7 +753,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>(3)2.9: Giving instructions</t>
+          <t>3.6 Reading</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -766,7 +766,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>(3)2.1: 0: Planning a game</t>
+          <t>3.7 Listening and writing</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -779,7 +779,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Unit 3 · Poems from around the world</t>
+          <t>Unit 4 · A good read</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>(3)3.1: Words that make pictures</t>
+          <t>4.1 Listening and speaking</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -805,7 +805,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>(3)3.2: Reading with expression</t>
+          <t>4.2 Reading</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -818,7 +818,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>(3)3.3: Performing a poem</t>
+          <t>4.3 Reading and writing</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -831,7 +831,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>(3)3.4: Onomatopoeia</t>
+          <t>4.4 Vocabulary</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -844,7 +844,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>(3)3.5: Writing a haiku</t>
+          <t>4.5 Speaking, listening and writing</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -857,7 +857,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>(3)3.6: Reviewing poems</t>
+          <t>4.6 Spelling</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -865,12 +865,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Subunit</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Unit 4 · Myths and legends</t>
+          <t>4.7 Speaking and listening</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>(3)4.1: Looking at a traditional story</t>
+          <t>4.8 Writing</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -896,7 +896,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>(3)4.2: What is a myth?</t>
+          <t>4.9 Grammar</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -904,12 +904,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Subunit</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>(3)4.3: Looking at pronouns</t>
+          <t>Unit 5 · Amazing journey</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -922,7 +922,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>(3)4.4: What is a legend?</t>
+          <t>5.1 Reading and speaking</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -935,7 +935,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>(3)4.5: Looking at paragraphs</t>
+          <t>5.2 Vocabulary</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -948,7 +948,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>(3)4.6: Joining sentences</t>
+          <t>5.3 Reading</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -961,7 +961,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>(3)4.7: Making links</t>
+          <t>5.4 Reading and writing</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>(3)4.8: Rewriting a myth</t>
+          <t>5.5 Spelling</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -987,7 +987,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>(3)4.9: Exploring a legend</t>
+          <t>5.6 Listening and speaking</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>(3)4.1: 0: Planning a legend</t>
+          <t>5.7 Writing</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>(3)4.1: 1: Writng a legend</t>
+          <t>5.8 Speaking</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>(3)4.1: 2: Improving your legend</t>
+          <t>5.9 Grammar</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Unit 5 · Writing to each other</t>
+          <t>Unit 6 · Myths and legends</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>(3)5.1: 0: Talking about mail</t>
+          <t>6.1 Reading and speaking</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>(3)5.1: What do we write?</t>
+          <t>6.2 Vocabulary</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>(3)5.2: Scanning or reading?</t>
+          <t>6.3 Listening and speaking</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>(3)5.3: Looking at synonyms</t>
+          <t>6.4 Grammar</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>(3)5.4: What does a letter look like?</t>
+          <t>6.5 Reading</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>(3)5.5: Looking at homophones</t>
+          <t>6.6 Writing</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1125,12 +1125,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Subunit</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>(3)5.6: A letter of complaint</t>
+          <t>Unit 7 · On stage</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>(3)5.7: Beginning and ending letters</t>
+          <t>7.1 Listening and speaking</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>(3)5.8: Looking at sentences in a letter</t>
+          <t>7.2 Reading instruction</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>(3)5.9: Other written communication</t>
+          <t>7.3 Reading and speaking</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>(3)5.1: 1: Writing a letter</t>
+          <t>7.4 Reading</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>(3)5.1: 2: Improving your letter</t>
+          <t>7.5 Grammar</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1203,12 +1203,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Subunit</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Unit 6 · Bringing stories alive</t>
+          <t>7.6 Writing</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>(3)6.1: Reading a playscript</t>
+          <t>7.7 Reading and writing</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>(3)6.2: Looking closely at a playscript</t>
+          <t>7.8 Vocabulary</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1242,12 +1242,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Subunit</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>(3)6.3: Writing dialogue and performing a play</t>
+          <t>Unit 8 · Amazing ships</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>(3)6.4: What happens next?</t>
+          <t>8.1 Reading</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>(3)6.5: Writing a playscript</t>
+          <t>8.2 Reading and writing</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>(3)6.6: Improving a playscript</t>
+          <t>8.3 Vocabulary</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1294,12 +1294,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Subunit</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Unit 7 · Going on an adventure</t>
+          <t>8.4 Grammar</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>(3)7.1: Reading an adventure</t>
+          <t>8.5 Spelling</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>(3)7.2: Story beginnings</t>
+          <t>8.6 Speaking and writing</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>(3)7.3: What happens next?</t>
+          <t>8.7 Speaking</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>(3)7.4: Character portraits</t>
+          <t>8.8 Reading and speaking</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1359,12 +1359,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Subunit</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>(3)7.5: Looking at chapters</t>
+          <t>Unit 9 · Sights, sounds and feeling</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>(3)7.6: Looking at verbs</t>
+          <t>9.1 Reading and speaking</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>(3)7.7: Looking in more detail</t>
+          <t>9.2 Writing</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>(3)7.9: More about paragraphs</t>
+          <t>9.3 Reading and listening</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>(3)7.1: 2: Improving your story</t>
+          <t>9.4 Vocabulary</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>(3)7.8: Setting and dialogue</t>
+          <t>9.5 Grammar and writing</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>(3)7.1: 1: Writing a story</t>
+          <t>9.6 Listening and speaking</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1450,12 +1450,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Subunit</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>(3)7.1: 0: Looking at stories</t>
+          <t>Term 1 Revision</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1463,12 +1463,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Unit 8 · Wonderful world</t>
+          <t>Term 1 Assessment</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1476,12 +1476,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Subunit</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>(3)8.1: Holidays</t>
+          <t>Term 1 School Activities</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1489,12 +1489,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Subunit</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>(3)8.2: In the library</t>
+          <t>Term 2 Revision</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1502,12 +1502,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Subunit</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>(3)8.3: Inside a non-fiction book</t>
+          <t>Term 2 Assessment</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1515,12 +1515,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Subunit</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>(3)8.4: Skimming and scanning</t>
+          <t>Term 2 School Activities</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1528,12 +1528,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Subunit</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>(3)8.5: Using paragraphs</t>
+          <t>Term 3 Revision</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1541,12 +1541,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Subunit</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>(3)8.6: Language features of information texts</t>
+          <t>Term 3 Assessment</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1554,171 +1554,15 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Subunit</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>(3)8.1: 0: Planning an information text</t>
+          <t>Term 3 School Activities</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Subunit</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>(3)8.1: 1: Writing an information text</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Subunit</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>(3)8.1: 2: Improving your text</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Subunit</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>(3)8.7: Non-fiction e-texts</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Subunit</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>(3)8.8: Planning a talk</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Subunit</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>(3)8.9: Giving your talk</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Unit 9 · Laughing allowed</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Subunit</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>(3)9.2: Wordplay in poetry</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Subunit</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>(3)9.3: Funny poems and limericks</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Subunit</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>(3)9.1: Riddles</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Subunit</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>(3)9.4: Calligrams and mnemonics</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Subunit</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>(3)9.5: Reviewing a poem</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Subunit</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>(3)9.6: Writing and performing a poem</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
